--- a/assets/constructions/examples/ctd_arbm_powerchuck.xlsx
+++ b/assets/constructions/examples/ctd_arbm_powerchuck.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
+  <dimension ref="A1:AM6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -604,11 +604,31 @@
           <t>adintws</t>
         </is>
       </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BT40-MLC25-120</t>
+          <t>BT50-MLC16-90</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -623,13 +643,13 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="F2" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="G2" t="n">
-        <v>62.5</v>
+        <v>51.5</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -639,12 +659,12 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>62.5</v>
+        <v>51.5</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>DER_RC-25</t>
+          <t>DER_RC-16</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -653,10 +673,10 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="T2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -672,13 +692,13 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>JIS_B_6339_MAS_403:BT40</t>
+          <t>JIS_B_6339_MAS_403:BT50</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>2.1</v>
+        <v>4.21</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -690,126 +710,144 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>DER_RC:HA-25</t>
-        </is>
+          <t>DER_RC:HA-16</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>402.93</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>33029.74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HSK100A-HPC25-115</t>
+          <t>BT50-C42-165HS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Фрезерные патроны HSK-A-HPC для высокоскоростной обработки</t>
+          <t>POWER MILLING CHUCK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="F3" t="n">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="G3" t="n">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>86</v>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>DER_RC-25</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>DEREK</t>
-        </is>
-      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="n">
-        <v>25</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="U3" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" t="n">
+        <v>42</v>
+      </c>
       <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+      <c r="X3" t="n">
+        <v>110</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Z3" t="b">
+        <v>0</v>
+      </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ISO_12164_1_2013:HSK100A</t>
+          <t>JIS_B_6339_MAS_403:BT50</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>3.45</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
+          <t>2021/YG1-TOOLING</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>DER_RC:HA-25</t>
-        </is>
-      </c>
+          <t>HA-42|YG1_K:42</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BT50-MLC42-165</t>
+          <t>SK50-MC20-200</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>AMATI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Силовые фрезерные патроны BT-MLC для тяжелых режимов обработки</t>
+          <t>Цанговый силовой патрон SK-MC</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="F4" t="n">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>87.5</v>
+        <v>55</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -818,87 +856,105 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
-        <v>87.5</v>
-      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>DER_RC-42</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>AMATI</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="T4" t="n">
-        <v>42</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>20</v>
+      </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+      <c r="Y4" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Z4" t="b">
+        <v>0</v>
+      </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>JIS_B_6339_MAS_403:BT50</t>
+          <t>DIN_69871:SK50</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="n">
-        <v>7.65</v>
-      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>DIN 69871</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
+          <t>2025 / AMATI Инструментальная и технологическая оснастка</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>DER_RC:HA-42</t>
-        </is>
+          <t>AMATI_RC:HA-20</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2968</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>36448.82</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BT40-MLC20-100</t>
+          <t>BT50-MC20-200</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>AMATI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Силовые фрезерные патроны BT-MLC для тяжелых режимов обработки</t>
+          <t>BT-MC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F5" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -907,31 +963,27 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
-        <v>53</v>
-      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>DER_RC-20</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>DEREK</t>
-        </is>
-      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
         <v>20</v>
       </c>
       <c r="T5" t="n">
         <v>20</v>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" t="n">
+        <v>16</v>
+      </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
+      <c r="Y5" t="n">
+        <v>15000</v>
+      </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
         <v>0</v>
@@ -941,32 +993,44 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>JIS_B_6339_MAS_403:BT40</t>
+          <t>JIS_B_6339_MAS_403:BT50</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="n">
-        <v>2.11</v>
-      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
+          <t>2025 / AMATI Инструментальная и технологическая оснастка</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>DER_RC:HA-20</t>
-        </is>
+          <t>HA-20</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>3850</v>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>47280.31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HSK100A-HPC16-115</t>
+          <t>SK50-HPC20-150</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -976,35 +1040,31 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Фрезерные патроны HSK-A-HPC для высокоскоростной обработки</t>
+          <t>Фрезерные патроны SK-HPC для высокоскоростной обработки</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="F6" t="n">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="G6" t="n">
-        <v>50</v>
+        <v>51.5</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>86</v>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>100</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>DER_RC-16</t>
+          <t>DER_RC-20</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1013,10 +1073,10 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="T6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
@@ -1032,13 +1092,13 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ISO_12164_1_2013:HSK100A</t>
+          <t>DIN_69871:SK50</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
-        <v>3.05</v>
+        <v>4.9</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1050,8 +1110,22 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>DER_RC:HA-16</t>
-        </is>
+          <t>DER_RC:HA-20</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>575.33</v>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>47162.04</v>
       </c>
     </row>
   </sheetData>
